--- a/outputs/Block2_2026_Fold_Targets_v12.xlsx
+++ b/outputs/Block2_2026_Fold_Targets_v12.xlsx
@@ -588,7 +588,7 @@
         <v>57</v>
       </c>
       <c r="F2">
-        <v>0.5213255079006773</v>
+        <v>0.5242150155486451</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -608,7 +608,7 @@
         <v>57</v>
       </c>
       <c r="F3">
-        <v>0.4506744920993228</v>
+        <v>0.447784984451355</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -668,7 +668,7 @@
         <v>57</v>
       </c>
       <c r="F6">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -688,7 +688,7 @@
         <v>57</v>
       </c>
       <c r="F7">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -748,7 +748,7 @@
         <v>57</v>
       </c>
       <c r="F10">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -808,7 +808,7 @@
         <v>57</v>
       </c>
       <c r="F13">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -828,7 +828,7 @@
         <v>57</v>
       </c>
       <c r="F14">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -908,7 +908,7 @@
         <v>57</v>
       </c>
       <c r="F18">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -1308,7 +1308,7 @@
         <v>58</v>
       </c>
       <c r="F38">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -1328,7 +1328,7 @@
         <v>58</v>
       </c>
       <c r="F39">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -1388,7 +1388,7 @@
         <v>58</v>
       </c>
       <c r="F42">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -1408,7 +1408,7 @@
         <v>58</v>
       </c>
       <c r="F43">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -1428,7 +1428,7 @@
         <v>57</v>
       </c>
       <c r="F44">
-        <v>0.5213255079006772</v>
+        <v>0.524215015548645</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -1448,7 +1448,7 @@
         <v>57</v>
       </c>
       <c r="F45">
-        <v>0.4506744920993228</v>
+        <v>0.447784984451355</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -1528,7 +1528,7 @@
         <v>57</v>
       </c>
       <c r="F49">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -1588,7 +1588,7 @@
         <v>57</v>
       </c>
       <c r="F52">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -1668,7 +1668,7 @@
         <v>57</v>
       </c>
       <c r="F56">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -1688,7 +1688,7 @@
         <v>57</v>
       </c>
       <c r="F57">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -1748,7 +1748,7 @@
         <v>57</v>
       </c>
       <c r="F60">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -1948,7 +1948,7 @@
         <v>57</v>
       </c>
       <c r="F70">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:6">
@@ -2068,7 +2068,7 @@
         <v>57</v>
       </c>
       <c r="F76">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="77" spans="1:6">
@@ -2148,7 +2148,7 @@
         <v>58</v>
       </c>
       <c r="F80">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="81" spans="1:6">
@@ -2168,7 +2168,7 @@
         <v>58</v>
       </c>
       <c r="F81">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="82" spans="1:6">
@@ -2228,7 +2228,7 @@
         <v>58</v>
       </c>
       <c r="F84">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -2248,7 +2248,7 @@
         <v>58</v>
       </c>
       <c r="F85">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="86" spans="1:6">
@@ -2268,7 +2268,7 @@
         <v>57</v>
       </c>
       <c r="F86">
-        <v>0.5211914221218962</v>
+        <v>0.5240801865837406</v>
       </c>
     </row>
     <row r="87" spans="1:6">
@@ -2288,7 +2288,7 @@
         <v>57</v>
       </c>
       <c r="F87">
-        <v>0.4505585778781038</v>
+        <v>0.4476698134162594</v>
       </c>
     </row>
     <row r="88" spans="1:6">
@@ -2328,7 +2328,7 @@
         <v>57</v>
       </c>
       <c r="F89">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:6">
@@ -2368,7 +2368,7 @@
         <v>57</v>
       </c>
       <c r="F91">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="92" spans="1:6">
@@ -2408,7 +2408,7 @@
         <v>57</v>
       </c>
       <c r="F93">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:6">
@@ -2428,7 +2428,7 @@
         <v>57</v>
       </c>
       <c r="F94">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="95" spans="1:6">
@@ -2508,7 +2508,7 @@
         <v>57</v>
       </c>
       <c r="F98">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="99" spans="1:6">
@@ -2528,7 +2528,7 @@
         <v>57</v>
       </c>
       <c r="F99">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="100" spans="1:6">
@@ -2588,7 +2588,7 @@
         <v>57</v>
       </c>
       <c r="F102">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="103" spans="1:6">
@@ -2988,7 +2988,7 @@
         <v>58</v>
       </c>
       <c r="F122">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="123" spans="1:6">
@@ -3008,7 +3008,7 @@
         <v>58</v>
       </c>
       <c r="F123">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="124" spans="1:6">
@@ -3068,7 +3068,7 @@
         <v>58</v>
       </c>
       <c r="F126">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="127" spans="1:6">
@@ -3088,7 +3088,7 @@
         <v>58</v>
       </c>
       <c r="F127">
-        <v>202</v>
+        <v>198</v>
       </c>
     </row>
     <row r="128" spans="1:6">
@@ -3108,7 +3108,7 @@
         <v>57</v>
       </c>
       <c r="F128">
-        <v>0.5191801354401807</v>
+        <v>0.5220577521101734</v>
       </c>
     </row>
     <row r="129" spans="1:6">
@@ -3128,7 +3128,7 @@
         <v>57</v>
       </c>
       <c r="F129">
-        <v>0.4488198645598194</v>
+        <v>0.4459422478898268</v>
       </c>
     </row>
     <row r="130" spans="1:6">
@@ -3268,7 +3268,7 @@
         <v>57</v>
       </c>
       <c r="F136">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="137" spans="1:6">
@@ -3288,7 +3288,7 @@
         <v>57</v>
       </c>
       <c r="F137">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="138" spans="1:6">
@@ -3408,7 +3408,7 @@
         <v>57</v>
       </c>
       <c r="F143">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -3428,7 +3428,7 @@
         <v>57</v>
       </c>
       <c r="F144">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="145" spans="1:6">
@@ -3828,7 +3828,7 @@
         <v>58</v>
       </c>
       <c r="F164">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="165" spans="1:6">
@@ -3848,7 +3848,7 @@
         <v>58</v>
       </c>
       <c r="F165">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="166" spans="1:6">
@@ -3908,7 +3908,7 @@
         <v>58</v>
       </c>
       <c r="F168">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="169" spans="1:6">
@@ -3928,7 +3928,7 @@
         <v>58</v>
       </c>
       <c r="F169">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="170" spans="1:6">
@@ -3948,7 +3948,7 @@
         <v>57</v>
       </c>
       <c r="F170">
-        <v>0.52038690744921</v>
+        <v>0.5232712127943137</v>
       </c>
     </row>
     <row r="171" spans="1:6">
@@ -3968,7 +3968,7 @@
         <v>57</v>
       </c>
       <c r="F171">
-        <v>0.44986309255079</v>
+        <v>0.4469787872056864</v>
       </c>
     </row>
     <row r="172" spans="1:6">
@@ -3988,7 +3988,7 @@
         <v>57</v>
       </c>
       <c r="F172">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="173" spans="1:6">
@@ -4048,7 +4048,7 @@
         <v>57</v>
       </c>
       <c r="F175">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="176" spans="1:6">
@@ -4108,7 +4108,7 @@
         <v>57</v>
       </c>
       <c r="F178">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="179" spans="1:6">
@@ -4128,7 +4128,7 @@
         <v>57</v>
       </c>
       <c r="F179">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="180" spans="1:6">
@@ -4248,7 +4248,7 @@
         <v>57</v>
       </c>
       <c r="F185">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="186" spans="1:6">
@@ -4268,7 +4268,7 @@
         <v>57</v>
       </c>
       <c r="F186">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="187" spans="1:6">
@@ -4348,7 +4348,7 @@
         <v>57</v>
       </c>
       <c r="F190">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="191" spans="1:6">
@@ -4428,7 +4428,7 @@
         <v>57</v>
       </c>
       <c r="F194">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="195" spans="1:6">
@@ -4488,7 +4488,7 @@
         <v>57</v>
       </c>
       <c r="F197">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="198" spans="1:6">
@@ -4508,7 +4508,7 @@
         <v>57</v>
       </c>
       <c r="F198">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="199" spans="1:6">
@@ -4648,7 +4648,7 @@
         <v>58</v>
       </c>
       <c r="F205">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="206" spans="1:6">
@@ -4668,7 +4668,7 @@
         <v>58</v>
       </c>
       <c r="F206">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="207" spans="1:6">
@@ -4688,7 +4688,7 @@
         <v>58</v>
       </c>
       <c r="F207">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="208" spans="1:6">
@@ -4708,7 +4708,7 @@
         <v>58</v>
       </c>
       <c r="F208">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="209" spans="1:6">
@@ -4728,7 +4728,7 @@
         <v>58</v>
       </c>
       <c r="F209">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="210" spans="1:6">
@@ -4748,7 +4748,7 @@
         <v>58</v>
       </c>
       <c r="F210">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="211" spans="1:6">
@@ -4768,7 +4768,7 @@
         <v>58</v>
       </c>
       <c r="F211">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Block2_2026_Fold_Targets_v12.xlsx
+++ b/outputs/Block2_2026_Fold_Targets_v12.xlsx
@@ -486,7 +486,7 @@
         <v>23</v>
       </c>
       <c r="F2">
-        <v>0.5284534340964659</v>
+        <v>0.5283780785444864</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -506,7 +506,7 @@
         <v>23</v>
       </c>
       <c r="F3">
-        <v>0.4435465659035341</v>
+        <v>0.4436219214555138</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -686,7 +686,7 @@
         <v>23</v>
       </c>
       <c r="F12">
-        <v>0.5284534340964659</v>
+        <v>0.5283780785444863</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -706,7 +706,7 @@
         <v>23</v>
       </c>
       <c r="F13">
-        <v>0.443546565903534</v>
+        <v>0.4436219214555137</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -886,7 +886,7 @@
         <v>23</v>
       </c>
       <c r="F22">
-        <v>0.5283175150033341</v>
+        <v>0.5282421788329265</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -906,7 +906,7 @@
         <v>23</v>
       </c>
       <c r="F23">
-        <v>0.4434324849966659</v>
+        <v>0.4435078211670735</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -1086,7 +1086,7 @@
         <v>23</v>
       </c>
       <c r="F32">
-        <v>0.526278728606357</v>
+        <v>0.5262036831595296</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -1106,7 +1106,7 @@
         <v>23</v>
       </c>
       <c r="F33">
-        <v>0.441721271393643</v>
+        <v>0.4417963168404705</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -1286,7 +1286,7 @@
         <v>23</v>
       </c>
       <c r="F42">
-        <v>0.5275020004445433</v>
+        <v>0.5274267805635677</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -1306,7 +1306,7 @@
         <v>23</v>
       </c>
       <c r="F43">
-        <v>0.4427479995554567</v>
+        <v>0.4428232194364323</v>
       </c>
     </row>
     <row r="44" spans="1:6">

--- a/outputs/Block2_2026_Fold_Targets_v12.xlsx
+++ b/outputs/Block2_2026_Fold_Targets_v12.xlsx
@@ -486,7 +486,7 @@
         <v>23</v>
       </c>
       <c r="F2">
-        <v>0.5283780785444864</v>
+        <v>0.5270809975722799</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -506,7 +506,7 @@
         <v>23</v>
       </c>
       <c r="F3">
-        <v>0.4436219214555138</v>
+        <v>0.4449190024277203</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -686,7 +686,7 @@
         <v>23</v>
       </c>
       <c r="F12">
-        <v>0.5283780785444863</v>
+        <v>0.5270809975722798</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -706,7 +706,7 @@
         <v>23</v>
       </c>
       <c r="F13">
-        <v>0.4436219214555137</v>
+        <v>0.4449190024277202</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -886,7 +886,7 @@
         <v>23</v>
       </c>
       <c r="F22">
-        <v>0.5282421788329265</v>
+        <v>0.5269454314720812</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -906,7 +906,7 @@
         <v>23</v>
       </c>
       <c r="F23">
-        <v>0.4435078211670735</v>
+        <v>0.4448045685279188</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -1086,7 +1086,7 @@
         <v>23</v>
       </c>
       <c r="F32">
-        <v>0.5262036831595296</v>
+        <v>0.5249119399691017</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -1106,7 +1106,7 @@
         <v>23</v>
       </c>
       <c r="F33">
-        <v>0.4417963168404705</v>
+        <v>0.4430880600308983</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -1286,7 +1286,7 @@
         <v>23</v>
       </c>
       <c r="F42">
-        <v>0.5274267805635677</v>
+        <v>0.5261320348708894</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -1306,7 +1306,7 @@
         <v>23</v>
       </c>
       <c r="F43">
-        <v>0.4428232194364323</v>
+        <v>0.4441179651291107</v>
       </c>
     </row>
     <row r="44" spans="1:6">

--- a/outputs/Block2_2026_Fold_Targets_v12.xlsx
+++ b/outputs/Block2_2026_Fold_Targets_v12.xlsx
@@ -486,7 +486,7 @@
         <v>23</v>
       </c>
       <c r="F2">
-        <v>0.5270809975722799</v>
+        <v>0.5302206593406594</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -506,7 +506,7 @@
         <v>23</v>
       </c>
       <c r="F3">
-        <v>0.4449190024277203</v>
+        <v>0.4417793406593407</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -686,7 +686,7 @@
         <v>23</v>
       </c>
       <c r="F12">
-        <v>0.5270809975722798</v>
+        <v>0.5302206593406593</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -706,7 +706,7 @@
         <v>23</v>
       </c>
       <c r="F13">
-        <v>0.4449190024277202</v>
+        <v>0.4417793406593407</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -886,7 +886,7 @@
         <v>23</v>
       </c>
       <c r="F22">
-        <v>0.5269454314720812</v>
+        <v>0.5300842857142858</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -906,7 +906,7 @@
         <v>23</v>
       </c>
       <c r="F23">
-        <v>0.4448045685279188</v>
+        <v>0.4416657142857143</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -1086,7 +1086,7 @@
         <v>23</v>
       </c>
       <c r="F32">
-        <v>0.5249119399691017</v>
+        <v>0.5280386813186814</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -1106,7 +1106,7 @@
         <v>23</v>
       </c>
       <c r="F33">
-        <v>0.4430880600308983</v>
+        <v>0.4399613186813187</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -1286,7 +1286,7 @@
         <v>23</v>
       </c>
       <c r="F42">
-        <v>0.5261320348708894</v>
+        <v>0.529266043956044</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -1306,7 +1306,7 @@
         <v>23</v>
       </c>
       <c r="F43">
-        <v>0.4441179651291107</v>
+        <v>0.4409839560439561</v>
       </c>
     </row>
     <row r="44" spans="1:6">

--- a/outputs/Block2_2026_Fold_Targets_v12.xlsx
+++ b/outputs/Block2_2026_Fold_Targets_v12.xlsx
@@ -486,7 +486,7 @@
         <v>23</v>
       </c>
       <c r="F2">
-        <v>0.5302206593406594</v>
+        <v>0.5286984957488554</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -506,7 +506,7 @@
         <v>23</v>
       </c>
       <c r="F3">
-        <v>0.4417793406593407</v>
+        <v>0.4433015042511447</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -686,7 +686,7 @@
         <v>23</v>
       </c>
       <c r="F12">
-        <v>0.5302206593406593</v>
+        <v>0.5286984957488554</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -706,7 +706,7 @@
         <v>23</v>
       </c>
       <c r="F13">
-        <v>0.4417793406593407</v>
+        <v>0.4433015042511446</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -886,7 +886,7 @@
         <v>23</v>
       </c>
       <c r="F22">
-        <v>0.5300842857142858</v>
+        <v>0.5285625136254631</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -906,7 +906,7 @@
         <v>23</v>
       </c>
       <c r="F23">
-        <v>0.4416657142857143</v>
+        <v>0.4431874863745368</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -1086,7 +1086,7 @@
         <v>23</v>
       </c>
       <c r="F32">
-        <v>0.5280386813186814</v>
+        <v>0.5265227817745803</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -1106,7 +1106,7 @@
         <v>23</v>
       </c>
       <c r="F33">
-        <v>0.4399613186813187</v>
+        <v>0.4414772182254198</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -1286,7 +1286,7 @@
         <v>23</v>
       </c>
       <c r="F42">
-        <v>0.529266043956044</v>
+        <v>0.52774662088511</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -1306,7 +1306,7 @@
         <v>23</v>
       </c>
       <c r="F43">
-        <v>0.4409839560439561</v>
+        <v>0.44250337911489</v>
       </c>
     </row>
     <row r="44" spans="1:6">
